--- a/data/client-intake/Client-Input-Dataset-v1.xlsx
+++ b/data/client-intake/Client-Input-Dataset-v1.xlsx
@@ -593,7 +593,7 @@
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>20 invented applications and the 57 pieces of information we ask the client for. The full dataset (App-Rationalization-Dummy-Dataset-v2.xlsx) has 126 columns for the same 20 applications; the other 69 are worked out by the tool from the 57 here - scores, pass and fail flags, the recommendation, the priority, the total cost of ownership, the savings arithmetic and the written rationale.</t>
+          <t>20 invented applications and the 57 pieces of information we ask the client for. The full dataset (App-Rationalization-Dummy-Dataset-v2.xlsx) has 125 columns for the same 20 applications; the other 68 are worked out by the tool from the 57 here - scores, pass and fail flags, the recommendation, the priority, the total cost of ownership, the savings arithmetic and the written rationale.</t>
         </is>
       </c>
     </row>
@@ -744,14 +744,14 @@
     <row r="31" ht="14" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>- App-Rationalization-Dummy-Dataset-v2.xlsx - the full 126-column dataset this was cut down from.</t>
+          <t>- App-Rationalization-Dummy-Dataset-v2.xlsx - the full 125-column dataset this was cut down from.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>- column-tiers.json - which of the 126 columns is asked for and which is derived, machine readable.</t>
+          <t>- column-tiers.json - which of the 125 columns is asked for and which is derived, machine readable.</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>V1 Increase Value. Criticality to revenue. 1 low, 5 high.</t>
+          <t>V1. Criticality to revenue: does the app carry money in or out? 1 low, 5 high.</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>V4 Criticality to patient care - does clinical work stop without it? WEIGHT 2 from v2 (Bina's Q3 ruling). Occupies the template's Enhance Services criterion. Named ov_enhance_services in v1. 5 = most critical.</t>
+          <t>V4 Criticality to patient care - does clinical work stop without it? WEIGHT 2 from v2 (Bina's Q3 ruling). Named ov_enhance_services in v1, before the criterion was renamed to say what it measures.</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>V5 Governance and Compliance. Regulatory alignment and owner-stated importance. WEIGHT 1 from v2; it held the double weight in v1. 5 = strongest alignment.</t>
+          <t>V5. Regulatory and trust alignment plus owner-stated importance. WEIGHT 1 from v2; it held the double weight in v1.</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>T2 (weight 2). Integration pattern, cloud readiness, architecture fit. 5 = best fit.</t>
+          <t>T2 (weight 2). Integration pattern, cloud readiness, architecture fit.</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -8501,7 +8501,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>T3. Incident and ticket volume; proactive vs reactive maintenance. 5 = most stable.</t>
+          <t>T3. Incident and ticket volume; proactive vs reactive maintenance.</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>T4. Vendor financial and roadmap viability. Scored here and nowhere else. 5 = most viable.</t>
+          <t>T4. Vendor financial and roadmap viability. Scored here and nowhere else.</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>T5. Customization debt and platform supportability. 5 = least debt.</t>
+          <t>T5. Customization debt and platform supportability.</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>R4, WEIGHT 0. The template's end-user signal, kept at the weight the template ships. 5 = best perceived quality.</t>
+          <t>R4, WEIGHT 0. End-user perceived quality. Collected and stored, contributes nothing.</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -8888,7 +8888,7 @@
     <row r="61">
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>57 columns asked for; 69 more are derived by the tool and are not in this workbook. See the full dataset's 'Data dictionary' sheet for those.</t>
+          <t>57 columns asked for; 68 more are derived by the tool and are not in this workbook. See the full dataset's 'Data dictionary' sheet for those.</t>
         </is>
       </c>
     </row>
@@ -11690,14 +11690,14 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Of the 69 derived columns, 17 come back identical from the client input alone and 52 do not. So no, the round trip does not fully reproduce v2.</t>
+          <t>Of the 68 derived columns, 17 come back identical from the client input alone and 51 do not. So no, the round trip does not fully reproduce v2.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="65" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>The reason is a single structural fact: generate_dataset.py only implements 38 of the 69 derivations. The other 31 derived columns are written by hand into the ROWS literals - the dataset author decided them, the code never computes them. When those 31 are supplied, all 38 implemented derivations reproduce v2 exactly, on every row, with zero mismatches. The engine is right; the pipeline in front of it is missing.</t>
+          <t>The reason is a single structural fact: generate_dataset.py only implements 37 of the 68 derivations. The other 31 derived columns are written by hand into the ROWS literals - the dataset author decided them, the code never computes them. When those 31 are supplied, all 37 implemented derivations reproduce v2 exactly, on every row, with zero mismatches. The engine is right; the pipeline in front of it is missing.</t>
         </is>
       </c>
     </row>
@@ -11780,14 +11780,14 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>The 21 knock-on failures</t>
+          <t>The 20 knock-on failures</t>
         </is>
       </c>
     </row>
     <row r="22" ht="78" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>These are computed correctly but from broken inputs, so they fail too, and they will all come right the moment the stages above exist: business_value_score, technical_health_score, cost_efficiency_score, c_pass, vtcr_key, infotech_template_disposition, retain_or_invest_basis, disposition, priority, rationale, confidence, redundancy_override_applied, suppressed_recommendation, suppression_reason, consolidation_saving, gross_saving_annual, net_saving_annual, net_saving_five_year, urgency_score, completeness_score, missing_fields.</t>
+          <t>These are computed correctly but from broken inputs, so they fail too, and they will all come right the moment the stages above exist: business_value_score, technical_health_score, cost_efficiency_score, c_pass, vtcr_key, retain_or_invest_basis, disposition, priority, rationale, confidence, redundancy_override_applied, suppressed_recommendation, suppression_reason, consolidation_saving, gross_saving_annual, net_saving_annual, net_saving_five_year, urgency_score, completeness_score, missing_fields.</t>
         </is>
       </c>
     </row>
